--- a/animal_rescue_application_forms/037_wildlife_rehabilitation_intake_form--animal_rescue_application_forms.xlsx
+++ b/animal_rescue_application_forms/037_wildlife_rehabilitation_intake_form--animal_rescue_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,146 +515,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>animal_rescue_application</t>
+          <t>species</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Animal Rescue Application</t>
+          <t>Animal Species</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>animal_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>Animal Status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rescue_location</t>
+          <t>rescue_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rescue_location</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter the location of the rescue event</t>
-        </is>
-      </c>
+          <t>Date of the Rescue Event</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>animal_status</t>
+          <t>species_count</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>animal_status</t>
+          <t>Number of Species</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>species_status</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>Description of the Event</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rescue_date</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter the date of the rescue event</t>
-        </is>
-      </c>
+          <t>Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,49 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>species_count</t>
+          <t>treatment_plans</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>species</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter the number of species involved in the rescue event</t>
-        </is>
-      </c>
+          <t>Treatment Plans</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>rehabilitation_facility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Please provide a detailed description of the event</t>
-        </is>
-      </c>
+          <t>Rehabilitation Facility</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -720,19 +704,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Describe any medical conditions affecting the animals</t>
-        </is>
-      </c>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -747,58 +727,58 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>treatment_plans</t>
+          <t>submitter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>treatment_plans</t>
+          <t>Submitter Information</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rehabilitation_facility</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rehabilitation_facility</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Contact Phone Number</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -811,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -839,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -857,24 +837,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Date the form was submitted</t>
-        </is>
-      </c>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -889,19 +865,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter your contact email</t>
-        </is>
-      </c>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -916,19 +888,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter your contact phone number</t>
-        </is>
-      </c>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -943,19 +911,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter your name</t>
-        </is>
-      </c>
+          <t>Zip</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -970,19 +934,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>fax_number</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>organization</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter your organization or agency</t>
-        </is>
-      </c>
+          <t>Fax Number</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -997,155 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter your address</t>
-        </is>
-      </c>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Enter your city</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter your state</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Enter your zip code</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fax_number</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>fax_number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter your fax number</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Enter your website url</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1162,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1331,114 +1152,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other_(please_describe)</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other (please describe)</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>species_status_choices</t>
+          <t>rehabilitation_facility_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wild</t>
+          <t>wildlife_rescue_and_rehabilitation_center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wild</t>
+          <t>Wildlife Rescue and Rehabilitation Center</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>species_status_choices</t>
+          <t>rehabilitation_facility_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>another_facility</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Domestic</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>rehabilitation_facility_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>wildlife_rescue_and_rehabilitation_center</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Wildlife Rescue and Rehabilitation Center</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rehabilitation_facility_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>another_center</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Another center</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>self-submitted</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Self-submitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submitted_by_another</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Submitted by another</t>
+          <t>Another facility</t>
         </is>
       </c>
     </row>
